--- a/Documentation/The Contradiction StoryBoard.xlsx
+++ b/Documentation/The Contradiction StoryBoard.xlsx
@@ -403,40 +403,40 @@
     <t xml:space="preserve">berjalan ke ujung lorong</t>
   </si>
   <si>
+    <t xml:space="preserve">taplak meja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bekerja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mendapatkan balasan dari samuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ke tempat samuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mengisi token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tempat tisu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jangan mandi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jangan sarapan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lorong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lampu plafon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jangan kerja</t>
+  </si>
+  <si>
     <t xml:space="preserve">belum dimulai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">taplak meja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bekerja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mendapatkan balasan dari samuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ke tempat samuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mengisi token</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tempat tisu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jangan mandi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jangan sarapan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lorong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lampu plafon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jangan kerja</t>
   </si>
   <si>
     <t xml:space="preserve">jangan melihat pesan samuel</t>
@@ -1950,11 +1950,11 @@
         <v>126</v>
       </c>
       <c r="E68" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1965,20 +1965,20 @@
         <v>15</v>
       </c>
       <c r="E69" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C70" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E70" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1986,11 +1986,11 @@
         <v>85</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E71" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1998,11 +1998,11 @@
         <v>88</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E72" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2010,11 +2010,11 @@
         <v>90</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E73" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2022,11 +2022,11 @@
         <v>92</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E74" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2037,20 +2037,20 @@
         <v>126</v>
       </c>
       <c r="E75" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C76" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="E76" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2058,11 +2058,11 @@
         <v>68</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E77" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2070,20 +2070,20 @@
         <v>6</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="D78" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="E78" s="5" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="E78" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Documentation/The Contradiction StoryBoard.xlsx
+++ b/Documentation/The Contradiction StoryBoard.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="205">
   <si>
     <t xml:space="preserve">no</t>
   </si>
@@ -52,6 +52,9 @@
     <t xml:space="preserve">done</t>
   </si>
   <si>
+    <t xml:space="preserve">belum dimulai</t>
+  </si>
+  <si>
     <t xml:space="preserve">bantal</t>
   </si>
   <si>
@@ -434,9 +437,6 @@
   </si>
   <si>
     <t xml:space="preserve">jangan kerja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">belum dimulai</t>
   </si>
   <si>
     <t xml:space="preserve">jangan melihat pesan samuel</t>
@@ -641,8 +641,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -725,7 +726,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -744,6 +745,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1077,7 +1082,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.88"/>
@@ -1086,6 +1091,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="58.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1128,221 +1134,278 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C9" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C11" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C14" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C15" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E15" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C16" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C17" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C19" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C20" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E20" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1350,13 +1413,13 @@
         <v>2</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1365,149 +1428,188 @@
       <c r="F21" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="G21" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C22" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E22" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C23" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E23" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E24" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C25" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C26" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C28" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E28" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E29" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C30" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C31" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C32" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C33" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1515,13 +1617,13 @@
         <v>3</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E34" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1530,233 +1632,293 @@
       <c r="F34" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="G34" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E35" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C36" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E36" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C37" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E37" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C38" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E38" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C39" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E39" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C40" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E40" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C41" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E41" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C42" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E42" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C43" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E43" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C44" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E44" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C45" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E45" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C46" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E46" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C47" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E47" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C48" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E48" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C49" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C50" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E50" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C51" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E51" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C52" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E52" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C53" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E53" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1764,13 +1926,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E54" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1779,161 +1941,203 @@
       <c r="F54" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="G54" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C55" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E55" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C56" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E56" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C57" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E57" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C58" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E58" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C59" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E59" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C60" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E60" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C61" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E61" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C62" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E62" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C63" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E63" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C64" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E64" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C65" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E65" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C66" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E66" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C67" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E67" s="5" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1941,128 +2145,158 @@
         <v>5</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E68" s="5" t="b">
+        <v>127</v>
+      </c>
+      <c r="E68" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="G68" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C69" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E69" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="E69" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C70" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E70" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <v>42</v>
+      </c>
+      <c r="E70" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C71" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E71" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <v>129</v>
+      </c>
+      <c r="E71" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C72" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E72" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <v>130</v>
+      </c>
+      <c r="E72" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C73" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E73" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <v>131</v>
+      </c>
+      <c r="E73" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C74" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E74" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="E74" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C75" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E75" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <v>127</v>
+      </c>
+      <c r="E75" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C76" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E76" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="E76" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C77" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E77" s="5" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <v>135</v>
+      </c>
+      <c r="E77" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2070,44 +2304,53 @@
         <v>6</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E78" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <v>138</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>138</v>
+        <v>9</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E79" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E79" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C80" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E80" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E80" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2117,9 +2360,12 @@
       <c r="D81" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E81" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E81" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2129,21 +2375,27 @@
       <c r="D82" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E82" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E82" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C83" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E83" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E83" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2154,41 +2406,50 @@
         <v>146</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E84" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E84" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>138</v>
+        <v>9</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C85" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="E85" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E85" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C86" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E86" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E86" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2198,9 +2459,12 @@
       <c r="D87" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E87" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E87" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2210,9 +2474,12 @@
       <c r="D88" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E88" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E88" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2222,33 +2489,42 @@
       <c r="D89" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E89" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E89" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C90" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E90" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E90" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C91" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E91" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E91" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2258,9 +2534,12 @@
       <c r="D92" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E92" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E92" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2270,9 +2549,12 @@
       <c r="D93" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E93" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E93" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2282,9 +2564,12 @@
       <c r="D94" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E94" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E94" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2294,9 +2579,12 @@
       <c r="D95" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E95" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E95" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2307,77 +2595,95 @@
         <v>166</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E96" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E96" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>138</v>
+        <v>9</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C97" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E97" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E97" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C98" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E98" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E98" s="6" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C99" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E99" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E99" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C100" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E100" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E100" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C101" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E101" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E101" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2387,45 +2693,57 @@
       <c r="D102" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E102" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E102" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C103" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E103" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E103" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C104" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E104" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E104" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C105" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E105" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E105" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2435,21 +2753,27 @@
       <c r="D106" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E106" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E106" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C107" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E107" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E107" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2459,9 +2783,12 @@
       <c r="D108" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E108" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E108" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2471,9 +2798,12 @@
       <c r="D109" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E109" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E109" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2483,21 +2813,27 @@
       <c r="D110" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E110" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E110" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C111" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E111" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E111" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2507,21 +2843,27 @@
       <c r="D112" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="E112" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E112" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C113" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E113" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E113" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2531,36 +2873,39 @@
       <c r="D114" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E114" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E114" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C115" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E115" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E115" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C116" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E116" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C117" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E117" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E117" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2573,21 +2918,21 @@
       <c r="C118" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E118" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E118" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>138</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C119" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E119" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E119" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2600,80 +2945,80 @@
       <c r="C120" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E120" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E120" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>138</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C121" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E121" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E121" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C122" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E122" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E122" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C123" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E123" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E123" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C124" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="E124" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E124" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C125" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E125" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E125" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C126" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E126" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E126" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C127" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E127" s="5" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E127" s="6" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2 F21 F34 F54 F68 F78 F84 F96 F118 F120" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:G2 G3:G97 F21 F34 F54 F68 F78 F84 F96 G98:G114 F118 F120" type="list">
       <formula1>"progress,done,belum dimulai,break"</formula1>
       <formula2>0</formula2>
     </dataValidation>
